--- a/data/keyrate_dates.xlsx
+++ b/data/keyrate_dates.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vasil\YandexDisk\project\LK_and_commets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vasil\YandexDisk\project\LK_and_commets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D403F6D5-B955-49BE-BB6B-97BFDF8B97A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C0BDD1B-9277-44FE-9B37-29F6FCEBFCF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12710" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{35B6687B-ADBD-4041-A0A7-3EB2F89F5FC7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{35B6687B-ADBD-4041-A0A7-3EB2F89F5FC7}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t>date</t>
   </si>
@@ -173,9 +173,6 @@
     <t>08.02.2019</t>
   </si>
   <si>
-    <t>01.04.2019</t>
-  </si>
-  <si>
     <t>26.04.2019</t>
   </si>
   <si>
@@ -296,9 +293,6 @@
     <t>15.09.2023</t>
   </si>
   <si>
-    <t>27.09.2023</t>
-  </si>
-  <si>
     <t>15.12.2023</t>
   </si>
   <si>
@@ -345,6 +339,15 @@
   </si>
   <si>
     <t>24.10.2025</t>
+  </si>
+  <si>
+    <t>27.10.2023</t>
+  </si>
+  <si>
+    <t>19.12.2025</t>
+  </si>
+  <si>
+    <t>13.02.2026</t>
   </si>
 </sst>
 </file>
@@ -717,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B257C07-B840-4B5C-9056-2E111641505A}">
-  <dimension ref="A1:A103"/>
+  <dimension ref="A1:A104"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
@@ -990,12 +993,12 @@
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
@@ -1020,7 +1023,7 @@
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
@@ -1044,12 +1047,12 @@
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+      <c r="A65" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" s="1" t="s">
+      <c r="A66" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1150,92 +1153,97 @@
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
